--- a/documents/competencesb1epreuveE5.xlsx
+++ b/documents/competencesb1epreuveE5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Boris EPHESTION\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Boris EPHESTION\Documents\BTS SIO\Stage\2ème année\Portfolio\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E25E77-4F99-41D8-B0AA-6A13C515569E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A22C4A-F052-42CE-A140-E9DA0ACAF7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="21600" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="55">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -98,9 +98,6 @@
 (intitulé et liste des documents et productions associés)</t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
-  </si>
-  <si>
     <t>Période (sous la forme du JJ/MM/AA au JJ/MM/AA)</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio :</t>
-  </si>
-  <si>
     <t>SESSION 2026</t>
   </si>
   <si>
@@ -167,9 +161,6 @@
     <t>Déploiement solution TeamsPhonie (Migration PABX)</t>
   </si>
   <si>
-    <t>Support utilisateur et résolution d'incidents (UniFLOW)</t>
-  </si>
-  <si>
     <t>Configuration et enrôlement de terminaux mobiles (MDM)</t>
   </si>
   <si>
@@ -192,6 +183,30 @@
   </si>
   <si>
     <t>semaine 7</t>
+  </si>
+  <si>
+    <t>N° candidat : 2251771120</t>
+  </si>
+  <si>
+    <t>Semestre 1</t>
+  </si>
+  <si>
+    <t>Semestre 2</t>
+  </si>
+  <si>
+    <t>tout le stage</t>
+  </si>
+  <si>
+    <t>Résolution d'incidents (UniFLOW)</t>
+  </si>
+  <si>
+    <t>Développer une application web de gestion de rapports de visites médicales (GSB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semestre 2 </t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : http://127.0.0.1:5500/Index.html</t>
   </si>
 </sst>
 </file>
@@ -201,7 +216,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -258,11 +273,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="16"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -663,7 +673,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -699,9 +709,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -802,14 +809,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
@@ -1145,91 +1144,91 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="8" width="18.6640625" style="1" customWidth="1"/>
     <col min="9" max="43" width="11.44140625" customWidth="1"/>
     <col min="44" max="16384" width="10.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="21"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="41"/>
+      <c r="A3" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="39"/>
+      <c r="H3" s="40"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="38"/>
+      <c r="A4" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="37"/>
       <c r="F4" s="11" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="18" t="s">
-        <v>27</v>
+      <c r="H4" s="17" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="32"/>
+      <c r="A5" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="31"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="28" t="s">
-        <v>19</v>
+      <c r="B6" s="27" t="s">
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>0</v>
@@ -1251,8 +1250,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
-      <c r="B7" s="29"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="5" t="s">
         <v>9</v>
       </c>
@@ -1308,16 +1307,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="23"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1356,19 +1355,23 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="15"/>
+        <v>35</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="14"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1407,23 +1410,25 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="14"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1461,14 +1466,24 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="15"/>
+      <c r="A11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="14"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1508,12 +1523,12 @@
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="15"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="14"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1553,12 +1568,12 @@
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="7"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="15"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="14"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1598,12 +1613,12 @@
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="7"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="15"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="14"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1643,12 +1658,12 @@
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="7"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="15"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="14"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1688,12 +1703,12 @@
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="7"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="15"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="14"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1733,12 +1748,12 @@
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
       <c r="B17" s="7"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="15"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="14"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1778,12 +1793,12 @@
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" s="7"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="15"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="14"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1821,16 +1836,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="27"/>
+      <c r="A19" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="26"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1869,21 +1884,23 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="14"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1922,21 +1939,23 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="14"/>
-      <c r="H21" s="15"/>
+        <v>38</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="13"/>
+      <c r="H21" s="14"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -1975,19 +1994,21 @@
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="14"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2026,19 +2047,21 @@
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="15"/>
+        <v>39</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="14"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2078,12 +2101,12 @@
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="15"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="14"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2123,12 +2146,12 @@
     <row r="25" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="15"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="14"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2168,12 +2191,12 @@
     <row r="26" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="15"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="14"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2211,16 +2234,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="27"/>
+      <c r="A27" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="26"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2259,26 +2282,24 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>26</v>
+        <v>40</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>24</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
@@ -2318,20 +2339,18 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="15" t="s">
-        <v>26</v>
+        <v>40</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="14" t="s">
+        <v>24</v>
       </c>
       <c r="I29"/>
       <c r="J29"/>
@@ -2371,25 +2390,25 @@
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="15"/>
+        <v>41</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="14"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2428,23 +2447,23 @@
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" s="15"/>
+        <v>41</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="14"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2483,17 +2502,17 @@
     </row>
     <row r="32" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="15"/>
+        <v>42</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="14"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2532,18 +2551,18 @@
     </row>
     <row r="33" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="15" t="s">
-        <v>26</v>
+        <v>43</v>
+      </c>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="14" t="s">
+        <v>24</v>
       </c>
       <c r="I33"/>
       <c r="J33"/>
@@ -2583,21 +2602,21 @@
     </row>
     <row r="34" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="17"/>
+        <v>44</v>
+      </c>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="16"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
@@ -2636,21 +2655,21 @@
     </row>
     <row r="35" spans="1:43" s="2" customFormat="1" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="H35" s="17"/>
+        <v>45</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="16"/>
       <c r="I35"/>
       <c r="J35"/>
       <c r="K35"/>
@@ -2689,21 +2708,21 @@
     </row>
     <row r="36" spans="1:43" customFormat="1" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="H36" s="17"/>
+        <v>46</v>
+      </c>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" s="16"/>
     </row>
     <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -2768,7 +2787,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="48" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="52" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>